--- a/partner_results/ifnano/ClassMissingGermanDefinition_ifnano.xlsx
+++ b/partner_results/ifnano/ClassMissingGermanDefinition_ifnano.xlsx
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sample [ifnano]</t>
+          <t>laser-induced breakdown spectroscopy [ifnano]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,7 +461,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A material entity, which is part of a larger set of the same material entity</t>
+          <t>Laser induced breakdown spectroscopy is a type of atomic emission spectroscopy which uses a highly energetic laser pulse as the excitation source. The laser is focused to form a plasma, which atomizes and excites samples. The Emission of these excited species is analyzed to identify and quantify the elements contained in the sample.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -469,22 +469,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>peak [ifnano]</t>
+          <t>styrene-butadiene rubber SBR [ifnano]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>In Spectroscopy, peaks are features of a spectrum. A peak comprise a restricted region of a spectrum, which is absorbed or emitted with high intensity. It is defined as a local maximum in the spectrum.</t>
+          <t>Families of synthetic rubbers derived from styrene and butadiene.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -492,22 +492,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>normalization [ifnano]</t>
+          <t>raw spectrum [ifnano]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Scaling spectra in order to get all data on approximately the same scale.</t>
+          <t>Unprocessed data obtained from spectrometric devices</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -515,22 +515,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>polymer composition [ifnano]</t>
+          <t>geometry correction [ifnano]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>proportion</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Jan Geweke</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The relative proportions of monomers that make up a particular chemical polymer (raw rubber).</t>
+          <t>In terms of digtal image procession: correction methods to compensate image errors caused by lense distorsion or perspective.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -538,22 +538,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>concentration [ifnano]</t>
+          <t>hydrogenated nitrile rubber HNBR [ifnano]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>rubber particle [chebi]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A quality of a substance in terms of its amount per unit volume in a mixture.</t>
+          <t>Highly Saturated Nitrile. A Higher performance solid rubber material than NBR, achieved through adding Hydrogen Atoms to the Butadiene Segments.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -561,22 +561,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fluororubber FKM [ifnano]</t>
+          <t>zinc [ifnano]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rubber particle [chebi]</t>
+          <t>metal atom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Is a family of fluorocarbon-based fluoroelastomer materials that contain vinylidene fluoride as a monomer.</t>
+          <t>The chemical element zinc</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -584,22 +584,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>raw spectrum [ifnano]</t>
+          <t>nitrile rubber NBR [ifnano]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Unprocessed data obtained from spectrometric devices</t>
+          <t>Known as nitrile butadiene rubber and acrylonitrile butadiene rubber, is a synthetic rubber derived from acrylonitrile (ACN) and butadiene.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -607,12 +607,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>laser-induced breakdown spectroscopy [ifnano]</t>
+          <t>standard deviation [ifnano]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Laser induced breakdown spectroscopy is a type of atomic emission spectroscopy which uses a highly energetic laser pulse as the excitation source. The laser is focused to form a plasma, which atomizes and excites samples. The Emission of these excited species is analyzed to identify and quantify the elements contained in the sample.</t>
+          <t>A measure of the amount of variation of a set of values.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -630,22 +630,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>butadiene rubber BR [ifnano]</t>
+          <t>FTIR spectroscopy [ifnano]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Yaman Alsalka (IFNANO)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Polybutadiene [butadiene rubber BR] is a synthetic rubber. Polybutadiene rubber is a polymer formed from the polymerization of the monomer 1,3-butadiene. Polybutadiene has a high resistance to wear and is used especially in the manufacture of tires.</t>
+          <t>Fourier transform infrared involves the probing of matter with infrared radiation. It is based on periodic changes in dipole moments caused by molecular vibrations during the absorption of IR radiation and gives spectroscopic fingerprints.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>nitrile rubber NBR [ifnano]</t>
+          <t>butyl rubber BIIR [ifnano]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Known as nitrile butadiene rubber and acrylonitrile butadiene rubber, is a synthetic rubber derived from acrylonitrile (ACN) and butadiene.</t>
+          <t>Is a synthetic rubber, a copolymer of isobutylene with isoprene</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -676,12 +676,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>functional group [ifnano]</t>
+          <t>normalization [ifnano]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>object aggregate</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>An atom or group of atoms within a molecule that has similar chemical properties whenever it appears in various compounds. Even if other parts of the molecule are quite different, certain functional groups tend to react in certain ways.</t>
+          <t>Scaling spectra in order to get all data on approximately the same scale.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -699,22 +699,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ATR-FTIR [ifnano]</t>
+          <t>sample [ifnano]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yamen Alsalka (IFNANO)</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>An attenuated total reflection accessory operates by measuring the changes that occur in a totally internally reflected infrared beam when the beam comes into contact with a sample.</t>
+          <t>A material entity, which is part of a larger set of the same material entity</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EPDM rubber [ifnano]</t>
+          <t>butadiene rubber BR [ifnano]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EPDM rubber (ethylene propylene diene monomer rubber) is a type of synthetic rubber that is composed of ethylidene norbornene (ENB), dicyclopentadiene (DCPD), and vinyl norbornene (VNB).</t>
+          <t>Polybutadiene [butadiene rubber BR] is a synthetic rubber. Polybutadiene rubber is a polymer formed from the polymerization of the monomer 1,3-butadiene. Polybutadiene has a high resistance to wear and is used especially in the manufacture of tires.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -745,22 +745,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>standard deviation [ifnano]</t>
+          <t>raw rubber samples [ifnano]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>raw material [hsh]</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka (IFNANO)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>A measure of the amount of variation of a set of values.</t>
+          <t>Natural and synthetic rubber materials that are modified and shaped into rubber products through the rubber extrusion process.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -768,22 +768,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>styrene-butadiene rubber SBR [ifnano]</t>
+          <t>photometry [ifnano]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Christoph Lenth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Families of synthetic rubbers derived from styrene and butadiene.</t>
+          <t>Measurement method using visible light to analyse the property of a substance</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -791,22 +791,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mooney viscosity [ifnano]</t>
+          <t>ATR-FTIR [ifnano]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Yamen Alsalka (IFNANO)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>The viscosity of rubber using a standard test method and Mooney Viscometer.</t>
+          <t>An attenuated total reflection accessory operates by measuring the changes that occur in a totally internally reflected infrared beam when the beam comes into contact with a sample.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -814,22 +814,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>photometry [ifnano]</t>
+          <t>EPDM rubber [ifnano]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Measurement method using visible light to analyse the property of a substance</t>
+          <t>EPDM rubber (ethylene propylene diene monomer rubber) is a type of synthetic rubber that is composed of ethylidene norbornene (ENB), dicyclopentadiene (DCPD), and vinyl norbornene (VNB).</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -837,22 +837,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>spectrum [ifnano]</t>
+          <t>functional group [ifnano]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>object aggregate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A graph that shows the intensity of radiation at different wavelengths or the response of the atomic or molecular system to different wavelengths of the radiation</t>
+          <t>An atom or group of atoms within a molecule that has similar chemical properties whenever it appears in various compounds. Even if other parts of the molecule are quite different, certain functional groups tend to react in certain ways.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -860,22 +860,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>processed spectrum [ifnano]</t>
+          <t>fluororubber FKM [ifnano]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>rubber particle [chebi]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Result of different mathematical processes conducted on raw Spectra. Processing steps include, e.g., normalization and baseline correction.</t>
+          <t>Is a family of fluorocarbon-based fluoroelastomer materials that contain vinylidene fluoride as a monomer.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -883,22 +883,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>butyl rubber BIIR [ifnano]</t>
+          <t>raman spectrum [ifnano]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Christoph Lenth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Is a synthetic rubber, a copolymer of isobutylene with isoprene</t>
+          <t>A graph presents a number of peaks, showing the intensity and wavelength position of the Raman scattered light, in which each peak corresponds to a specific molecular bond vibration.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -906,18 +906,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>photometric measurement process [ifnano]</t>
+          <t>peak [ifnano]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sven Schwabe (IFNANO)</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Measurement using photometry</t>
+          <t>In Spectroscopy, peaks are features of a spectrum. A peak comprise a restricted region of a spectrum, which is absorbed or emitted with high intensity. It is defined as a local maximum in the spectrum.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -925,7 +929,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Raman spectroscopy [ifnano]</t>
+          <t>digital image processing [ifnano]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -933,14 +937,10 @@
           <t>plan specification</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Georgios Ctistis</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A non-destructive light scattering technique that provides detailed information about the chemical structure upon the interaction of light with the chemical bonds within a material based on periodic changes of polarizabilities, usually manifested as energy loss (gain) with respect to the incident light.</t>
+          <t>The use of a digital computer to process digital images through an algorithm.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -948,7 +948,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>analytical target [ifnano]</t>
+          <t>processed spectrum [ifnano]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>The information represented by one or more variables, which has to be predicted by data analysis in instrumental analytics</t>
+          <t>Result of different mathematical processes conducted on raw Spectra. Processing steps include, e.g., normalization and baseline correction.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -971,12 +971,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>zinc [ifnano]</t>
+          <t>distribution quality [ifnano]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>metal atom</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The chemical element zinc</t>
+          <t>A quality of a sample in terms of homogenity, or the distribution of concentration of a specific component in a mixture, in a macroscopic body.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -994,22 +994,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>raman spectrum [ifnano]</t>
+          <t>polyisoprene IR [ifnano]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>synthetic rubber [dik]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Christoph Lenth</t>
+          <t>Yamen Alsalka</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A graph presents a number of peaks, showing the intensity and wavelength position of the Raman scattered light, in which each peak corresponds to a specific molecular bond vibration.</t>
+          <t>A synthetic cis-1,4-polyisoprene, made by the industrial polymerisation of isoprene.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1017,88 +1017,88 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Raman spectroscopy [ifnano]</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>plan specification</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Georgios Ctistis</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A non-destructive light scattering technique that provides detailed information about the chemical structure upon the interaction of light with the chemical bonds within a material based on periodic changes of polarizabilities, usually manifested as energy loss (gain) with respect to the incident light.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mooney viscosity [ifnano]</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>intensive quality</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Yamen Alsalka</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>The viscosity of rubber using a standard test method and Mooney Viscometer.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>monomer [ifnano]</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>molecular entity</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Asubstance which is capable of forming covalent bonds with a
 sequence of additional like or unlike molecules under the conditions of the relevant polymerforming reaction used for the particular process</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>geometry correction [ifnano]</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Jan Geweke</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>In terms of digtal image procession: correction methods to compensate image errors caused by lense distorsion or perspective.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>raw rubber samples [ifnano]</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>raw material [hsh]</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yamen Alsalka (IFNANO)</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Natural and synthetic rubber materials that are modified and shaped into rubber products through the rubber extrusion process.</t>
-        </is>
-      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>polyisoprene IR [ifnano]</t>
+          <t>concentration [ifnano]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>synthetic rubber [dik]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Sven Schwabe (IFNANO)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A synthetic cis-1,4-polyisoprene, made by the industrial polymerisation of isoprene.</t>
+          <t>A quality of a substance in terms of its amount per unit volume in a mixture.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1106,22 +1106,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hydrogenated nitrile rubber HNBR [ifnano]</t>
+          <t>polymer composition [ifnano]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>rubber particle [chebi]</t>
+          <t>proportion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yamen Alsalka</t>
+          <t>Christoph Lenth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Highly Saturated Nitrile. A Higher performance solid rubber material than NBR, achieved through adding Hydrogen Atoms to the Butadiene Segments.</t>
+          <t>The relative proportions of monomers that make up a particular chemical polymer (raw rubber).</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1129,22 +1129,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FTIR spectroscopy [ifnano]</t>
+          <t>photometric measurement process [ifnano]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yaman Alsalka (IFNANO)</t>
-        </is>
-      </c>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fourier transform infrared involves the probing of matter with infrared radiation. It is based on periodic changes in dipole moments caused by molecular vibrations during the absorption of IR radiation and gives spectroscopic fingerprints.</t>
+          <t>Measurement using photometry</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1152,22 +1148,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>distribution quality [ifnano]</t>
+          <t>spectrum [ifnano]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sven Schwabe (IFNANO)</t>
+          <t>Christoph Lenth</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A quality of a sample in terms of homogenity, or the distribution of concentration of a specific component in a mixture, in a macroscopic body.</t>
+          <t>A graph that shows the intensity of radiation at different wavelengths or the response of the atomic or molecular system to different wavelengths of the radiation</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1175,18 +1171,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>digital image processing [ifnano]</t>
+          <t>analytical target [ifnano]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>plan specification</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Christoph Lenth</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>The use of a digital computer to process digital images through an algorithm.</t>
+          <t>The information represented by one or more variables, which has to be predicted by data analysis in instrumental analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
